--- a/config/yunying/mid_autumn_draw_tasks.xlsx
+++ b/config/yunying/mid_autumn_draw_tasks.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="mid_autumn_draw_tasks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mid_autumn_draw_tasks" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1230,10 +1230,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ゲームログイン</t>
+          <t>游戏登录</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1246,7 +1245,6 @@
           <t>Log in to game</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>당일 게임 로그인</t>
@@ -1279,10 +1277,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>金貨回収を5回</t>
+          <t>金币回收5次</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1295,7 +1292,6 @@
           <t>Perform Gold Recovery 5 times</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>당일 보물단지 5회</t>
@@ -1328,10 +1324,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>本日5回アリーナに挑戦</t>
+          <t>今天第5次挑战竞技场</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1344,7 +1339,6 @@
           <t>Challenge Arena 5 times today</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>당일 아레나 도전 5회</t>
@@ -1356,19 +1350,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -1390,10 +1372,9 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>本日スタミナを100消費</t>
+          <t>今天消耗100体力</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1406,7 +1387,6 @@
           <t>Spend 100 Stamina today</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>당일 체력 100 소모</t>
@@ -1439,10 +1419,9 @@
           <t>300</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>本日スタミナを300消費</t>
+          <t>今日消耗300体力</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1455,7 +1434,6 @@
           <t>Spend 300 Stamina today</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>당일 체력 300 소모</t>
@@ -1488,10 +1466,9 @@
           <t>600</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>本日スタミナを600消費</t>
+          <t>今日消耗600体力</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1504,7 +1481,6 @@
           <t>Spend 600 Stamina today</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>당일 체력 600 소모</t>
@@ -1537,10 +1513,9 @@
           <t>900</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>本日スタミナを900消費</t>
+          <t>今天消耗900体力</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1553,7 +1528,6 @@
           <t>Spend 900 Stamina today</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>당일 체력 900 소모</t>
@@ -1586,10 +1560,9 @@
           <t>1200</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>本日スタミナを1200消費</t>
+          <t>今天消耗1200体力</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1602,7 +1575,6 @@
           <t>Spend 1,200 Stamina today</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>당일 체력 1200 소모</t>
@@ -1614,19 +1586,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1648,10 +1608,9 @@
           <t>60</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>本日60ダイヤをチャージ</t>
+          <t>今日充值60颗钻石</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1664,7 +1623,6 @@
           <t>Top up 60 Diamonds today</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>당일 60 다이아 충전</t>
@@ -1697,10 +1655,9 @@
           <t>300</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>本日300ダイヤをチャージ</t>
+          <t>今日充值300颗钻石</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1713,7 +1670,6 @@
           <t>Top up 300 Diamonds today</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>당일 300 다이아 충전</t>
@@ -1725,19 +1681,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -1759,10 +1703,9 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>本日200ダイヤを消費</t>
+          <t>今日消费200颗钻石</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1775,7 +1718,6 @@
           <t>Spend 200 Diamonds today</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>당일 200 다이아 소모</t>
@@ -1808,10 +1750,9 @@
           <t>500</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>本日500ダイヤを消費</t>
+          <t>今日消费500颗钻石</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1824,7 +1765,6 @@
           <t>Spend 500 Diamonds today</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>당일 500 다이아 소모</t>
